--- a/test/samples/system/GreenTable/Bcm/TUR.xlsx
+++ b/test/samples/system/GreenTable/Bcm/TUR.xlsx
@@ -6,12 +6,12 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="INPUT" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OUTPUT" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RECEIVE" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEND" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'INPUT'!$A$1:$K$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'OUTPUT'!$A$1:$K$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'RECEIVE'!$A$1:$K$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'SEND'!$A$1:$K$2</definedName>
   </definedNames>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
@@ -591,8 +591,6 @@
           <t>Position lamp test</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
           <t>PositionActive</t>
@@ -754,8 +752,6 @@
           <t>Power mode test</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
           <t>PowerMode</t>

--- a/test/samples/system/GreenTable/Bcm/TUR.xlsx
+++ b/test/samples/system/GreenTable/Bcm/TUR.xlsx
@@ -6,12 +6,12 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RECEIVE" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEND" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="R-Port" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="P-Port" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'RECEIVE'!$A$1:$K$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'SEND'!$A$1:$K$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'R-Port'!$A$1:$K$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'P-Port'!$A$1:$K$2</definedName>
   </definedNames>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>

--- a/test/samples/system/GreenTable/Bcm/TUR.xlsx
+++ b/test/samples/system/GreenTable/Bcm/TUR.xlsx
@@ -6,12 +6,12 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="INPUT" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OUTPUT" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="R-Port" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="P-Port" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'INPUT'!$A$1:$K$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'OUTPUT'!$A$1:$K$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'R-Port'!$A$1:$K$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'P-Port'!$A$1:$K$2</definedName>
   </definedNames>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
@@ -591,8 +591,6 @@
           <t>Position lamp test</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
           <t>PositionActive</t>
@@ -754,8 +752,6 @@
           <t>Power mode test</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
           <t>PowerMode</t>
